--- a/dataset/DIP.xlsx
+++ b/dataset/DIP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="251">
   <si>
     <t>entry</t>
   </si>
@@ -43,6 +43,552 @@
     <t>test</t>
   </si>
   <si>
+    <t>CCC(C)=O</t>
+  </si>
+  <si>
+    <t>ZWEHNKRNPOVVGH-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>H. C. Brown, J. Chandrasekharan, P. V. Ramachandran, J. Am. Chem. Soc. 1988, 110, 1539-1546.</t>
+  </si>
+  <si>
+    <t>CCCCCCC(C)=O</t>
+  </si>
+  <si>
+    <t>ZPVFWPFBNIEHGJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>KWOLFJPFCHCOCG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>KRIOVPPHQSLHCZ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>FFSAXUULYPJSKH-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>QQXJNLYVPPBERR-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)C(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>BSMGLVDZZMBWQB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)C(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>OECPUBRNDKXFDX-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCc2ccccc21</t>
+  </si>
+  <si>
+    <t>QNXSIUBBGPHDDE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCCc2ccccc21</t>
+  </si>
+  <si>
+    <t>XHLHPRDBBAGVEG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccc2ccccc2c1</t>
+  </si>
+  <si>
+    <t>XSAYZAUNJMRRIR-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1cccnc1</t>
+  </si>
+  <si>
+    <t>WEGYGNROSJDEIW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1cccs1</t>
+  </si>
+  <si>
+    <t>WYJOVVXUZNRJQY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C(C)C(C)=O</t>
+  </si>
+  <si>
+    <t>FNENWZWNOPCZGK-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CBr)c1ccccc1</t>
+  </si>
+  <si>
+    <t>LIGACIXOYTUXAW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>M. Srebr, P. V. Ramachandran, H. C. Brown, J. Org. Chem. 1988, 53, 2916-2920.</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccc(Br)cc1</t>
+  </si>
+  <si>
+    <t>WYECURVXVYPVAT-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCCl)c1ccccc1</t>
+  </si>
+  <si>
+    <t>KTJRGPZVSKWRTJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCC(=O)c1ccc(Cl)cc1</t>
+  </si>
+  <si>
+    <t>ADCYRBXQAJXJTD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCl)c1ccc(Cl)cc1Cl</t>
+  </si>
+  <si>
+    <t>VYWPPRLJNVHPEU-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCC(=O)c1ccc(Cl)cc1-c1ccc(Br)cc1</t>
+  </si>
+  <si>
+    <t>JGUYBMKIKPABSY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>RIFKADJTWUGDOV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>H. C. Brown, P. V. Ramachandran, J. Org. Chem. 1989, 54, 4504-4511.</t>
+  </si>
+  <si>
+    <t>CCC(=O)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>AMHOPTNGSNYSBL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCC(=O)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>UYMHLXHLPQIDMA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C1CCCC1</t>
+  </si>
+  <si>
+    <t>LKENTYLPIUIMFG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCCC1(c1ccccc1)c1ccccc1</t>
+  </si>
+  <si>
+    <t>CBOPQVXWIKRPKD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>D. Potin, F Dumas, J D'Angelo, J. Am. Chem. Soc. 1990, 112, 3483.</t>
+  </si>
+  <si>
+    <t>COCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>YRNDGUSDBCARGC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>H. C. Brown, P. V. Ramachandran, Acc. Chem. Res. 1992, 25, 16-24.</t>
+  </si>
+  <si>
+    <t>CCC(=O)c1ccc([N+](=O)[O-])cc1</t>
+  </si>
+  <si>
+    <t>QHTSEJJUUBOESF-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccccc1Br</t>
+  </si>
+  <si>
+    <t>PIMNFNXBTGPCIL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCCl)c1ccc(Br)cc1</t>
+  </si>
+  <si>
+    <t>SYWQQEVHZPPLNQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCC(=O)c1cc(OC)ccc1OC</t>
+  </si>
+  <si>
+    <t>DKVCHMQHUMLKPO-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C(C)(C)C</t>
+  </si>
+  <si>
+    <t>PJGSXYOJTGTZAV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C(C)(C)C(C)=O</t>
+  </si>
+  <si>
+    <t>NVAHZHOCRQCUBY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC1(C)CCCC1=O</t>
+  </si>
+  <si>
+    <t>FTGZMZBYOHMEPS-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)[C@]1(C)CCCC1=O</t>
+  </si>
+  <si>
+    <t>TZHZMYGNHVTEFA-MRVPVSSYSA-N</t>
+  </si>
+  <si>
+    <t>CC1(C)CCCCC1=O</t>
+  </si>
+  <si>
+    <t>KNSPBSQWRKKAPI-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCCC12CCCC2</t>
+  </si>
+  <si>
+    <t>QRYJGVNQNLCGGZ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCC#CC(=O)C(C)(C)C</t>
+  </si>
+  <si>
+    <t>XVKCCRCIQKVMPK-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCC#CC(=O)C(C)(C)c1ccccc1</t>
+  </si>
+  <si>
+    <t>HJPJVTHMENRJQA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C=CCC(C)(C)C(=O)C#CCCCCCCCC</t>
+  </si>
+  <si>
+    <t>TYGJBMAZCWFZFC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCC#CC(=O)C(C)(C)CCC</t>
+  </si>
+  <si>
+    <t>QRJXIADOTSHIRY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCC#CC(=O)C(C)(CC)CCC</t>
+  </si>
+  <si>
+    <t>MMUXSGDQWCOFKS-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCC#CC(=O)C(CC)(CC)CCC</t>
+  </si>
+  <si>
+    <t>ZKJADHMQUMUECR-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C(C)C</t>
+  </si>
+  <si>
+    <t>SYBYTAAJFKOIEJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCl)c1ccccc1</t>
+  </si>
+  <si>
+    <t>IMACFCSSMIZSPP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)/C=C/c1ccccc1</t>
+  </si>
+  <si>
+    <t>BWHOZHOGCMHOBV-BQYQJAHWSA-N</t>
+  </si>
+  <si>
+    <t>O=C1C=CCCC1</t>
+  </si>
+  <si>
+    <t>FWFSEYBSWVRWGL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C#Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>UPEUQDJSUFHFQP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C#CC(C)=O</t>
+  </si>
+  <si>
+    <t>XRGPFNGLRSIPSA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>P. V. Ramachandran, et al., J. Org. Chem. 1992, 57, 2379-2386</t>
+  </si>
+  <si>
+    <t>CCC(=O)C#Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>XAJIQJSLJKBJTP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)C(=O)C#Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>AOOHPXMHKBITKB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)C(=O)C#CC1CCCCC1</t>
+  </si>
+  <si>
+    <t>SCDHTAAYEHJTGD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)C(=O)C#CC1CCCCC1</t>
+  </si>
+  <si>
+    <t>MSRORZBOBVAASL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCCCl)c1ccc(F)cc1</t>
+  </si>
+  <si>
+    <t>HXAOUYGZEOZTJO-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>P. V. Ramachandran, B Gong, H. C. Brown, Tetrahedron Asymm. 1993, 4, 2399-2400.</t>
+  </si>
+  <si>
+    <t>O=C(c1cccc2ccccc12)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>VQCWOGKZDGCRES-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>P. V. AV Teodorovic, . H.C Brown, Tetra. h.edron, 1993, 49, 1725-1738.</t>
+  </si>
+  <si>
+    <t>O=C(c1ccc2ccccc2c1)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>JWQLBVFFLIHXHA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1c2ccccc2cc2ccccc12)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>MNCMBBIFTVWHIP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)C(F)(F)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>VUBUXALTYMBEQO-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)C(F)(F)C(F)(F)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>UKYZDGAVBNKBPQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCC(=O)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>NDQOKFMZSIKVBG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCC(=O)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>OQHGRUHRHLFMBX-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(C1CCCCC1)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>RPTSLLGEWZGTHJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)C(=O)C#Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>QXGIWMOPVOXYCX-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>P. V. Ramachandran, B. Gong, A. V. Teodorovic, Tetrahedron, 1994, 5, 1061-1074.</t>
+  </si>
+  <si>
+    <t>O=C(C#Cc1ccccc1)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>LISOVATZGSPQOC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(C#Cc1ccccc1)CF</t>
+  </si>
+  <si>
+    <t>KXSOGUNMZUFDEV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(C#Cc1ccccc1)C(F)F</t>
+  </si>
+  <si>
+    <t>PWFHYGISSIMQKI-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(C#Cc1ccccc1)C(F)(F)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>VCARCPYEXCPAJO-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(C#Cc1ccccc1)C(F)(F)C(F)(F)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>JLQHDTDAQBOUBB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC#CC(=O)CF</t>
+  </si>
+  <si>
+    <t>RRJHAIWETICRET-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC#CC(=O)C(F)F</t>
+  </si>
+  <si>
+    <t>CDGZCBOPYKCCLD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC#CC(=O)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>XAXKYUYIYBKVHR-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC#CC(=O)C(F)(F)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>MKMFBYKRUQCCTG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC#CC(=O)C(F)(F)C(F)(F)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>DPQDBEUDQJLCFS-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)CF</t>
+  </si>
+  <si>
+    <t>ULGQTMJOCRMHRB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>P. V. Ramachandran, A. V. Teodorovic, B. Gong, H. C. Brown, Tetrahedron: Asymmetry, 1994, 5, 1075-1086.</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)C(F)F</t>
+  </si>
+  <si>
+    <t>PFOYLZWXMOUFRP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>DPXNESFWZZBKJM-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1cccc(OC)c1C(C)=O</t>
+  </si>
+  <si>
+    <t>XEUGKOFTNAYMMX-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>P. V. Ramachandran, B Gong, H. C. Brown, Tetrahedron Lett. 1994, 35, 2141-2144.</t>
+  </si>
+  <si>
+    <t>COc1ccc(OC)c(C(C)=O)c1</t>
+  </si>
+  <si>
+    <t>FAXUIYJKGGUCBO-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccc(C)cc1C(C)=O</t>
+  </si>
+  <si>
+    <t>FHIOYMGCAXTUGF-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccc(F)cc1C(C)=O</t>
+  </si>
+  <si>
+    <t>CNVGMLMIQIPAFY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1c(Cl)cc(Cl)cc1C(C)=O</t>
+  </si>
+  <si>
+    <t>MLXBLQUBVDCARQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)c1cc(OC)cc(OC)c1C(C)=O</t>
+  </si>
+  <si>
+    <t>LUWXCCCGOWDRJL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccccc1C(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>CSUUDNFYSFENAE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Shieh, Wen-Chung, William R. Cantrell Jr, and John A. Carlson. Tetrahedron letters, 1995, 36, 3797-3800.</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)c1ccccc1F</t>
+  </si>
+  <si>
+    <t>DWFDQVMFSLLMPE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)c1ccccc1Cl</t>
+  </si>
+  <si>
+    <t>VMHYWKBKHMYRNF-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Cc1ccccc1C(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>CKGKXGQVRVAKEA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
     <t>O=C(CBr)C(F)(F)F</t>
   </si>
   <si>
@@ -52,87 +598,6 @@
     <t>P. V. Ramachandran, B. Gong, H. C. Brown, The Journal of Organic Chemistry, 1995,  60, 41-46.</t>
   </si>
   <si>
-    <t>COc1cccc(OC)c1C(C)=O</t>
-  </si>
-  <si>
-    <t>XEUGKOFTNAYMMX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>P. V. Ramachandran, B Gong, H. C. Brown, Tetrahedron Lett. 1994, 35, 2141-2144.</t>
-  </si>
-  <si>
-    <t>O=C(CCCl)c1ccccc1</t>
-  </si>
-  <si>
-    <t>KTJRGPZVSKWRTJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>M. Srebr, P. V. Ramachandran, H. C. Brown, J. Org. Chem. 1988, 53, 2916-2920.</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C(F)(F)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>VUBUXALTYMBEQO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>P. V. AV Teodorovic, . H.C Brown, Tetra. h.edron, 1993, 49, 1725-1738.</t>
-  </si>
-  <si>
-    <t>CCCCCCCCC#CC(=O)C(C)(C)c1ccccc1</t>
-  </si>
-  <si>
-    <t>HJPJVTHMENRJQA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>H. C. Brown, P. V. Ramachandran, Acc. Chem. Res. 1992, 25, 16-24.</t>
-  </si>
-  <si>
-    <t>CC(C)(C)C(=O)C#Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>QXGIWMOPVOXYCX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>P. V. Ramachandran, B. Gong, A. V. Teodorovic, Tetrahedron, 1994, 5, 1061-1074.</t>
-  </si>
-  <si>
-    <t>CCCCC#CC(=O)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>XAXKYUYIYBKVHR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC#CC(=O)C(F)(F)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>MKMFBYKRUQCCTG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)C#Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>AOOHPXMHKBITKB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>P. V. Ramachandran, et al., J. Org. Chem. 1992, 57, 2379-2386</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>QQXJNLYVPPBERR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>H. C. Brown, J. Chandrasekharan, P. V. Ramachandran, J. Am. Chem. Soc. 1988, 110, 1539-1546.</t>
-  </si>
-  <si>
-    <t>CCCCCCCCC#CC(=O)C(C)(C)CCC</t>
-  </si>
-  <si>
-    <t>QRJXIADOTSHIRY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
     <t>COC(=O)c1ccccc1C(C)=O</t>
   </si>
   <si>
@@ -142,49 +607,121 @@
     <t>P. V. Ramachandran, G. M. Chen, H. C. Brown, Tetrahedron letters, 1996, 37, 2205-2208.</t>
   </si>
   <si>
-    <t>O=C(C#Cc1ccccc1)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>LISOVATZGSPQOC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COC(=O)c1cc(OC)cc(OC)c1C(C)=O</t>
-  </si>
-  <si>
-    <t>LUWXCCCGOWDRJL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)c1cc(OC)ccc1OC</t>
-  </si>
-  <si>
-    <t>DKVCHMQHUMLKPO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(C#Cc1ccccc1)CF</t>
-  </si>
-  <si>
-    <t>KXSOGUNMZUFDEV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(C#Cc1ccccc1)C(F)F</t>
-  </si>
-  <si>
-    <t>PWFHYGISSIMQKI-UHFFFAOYSA-N</t>
-  </si>
-  <si>
     <t>CCC(=O)c1ccccc1C(=O)OC</t>
   </si>
   <si>
     <t>PJVVSYKDAYJZCV-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>CC(=O)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>RIFKADJTWUGDOV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>H. C. Brown, P. V. Ramachandran, J. Org. Chem. 1989, 54, 4504-4511.</t>
+    <t>CCCCC(=O)c1ccccc1C(=O)OC</t>
+  </si>
+  <si>
+    <t>QTUYJWKFWYJIOM-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)c1ccccc1C(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>NQSMEZJWJJVYOI-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccccc1C(C)=O</t>
+  </si>
+  <si>
+    <t>DWPLEOPKBWNPQV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>M. Zhao, et al., Tetrahedron Lett. 1997, 38, 2641-2644.</t>
+  </si>
+  <si>
+    <t>COc1cccc(C(C)=O)c1</t>
+  </si>
+  <si>
+    <t>BAYUSCHCCGXLAY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccc(C(C)=O)cc1</t>
+  </si>
+  <si>
+    <t>NTPLXRHDUXRPNE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccc(C(C)=O)cc1OC</t>
+  </si>
+  <si>
+    <t>IQZLUWLMQNGTIW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)C(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>YLHXLHGIAMFFBU-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>P. V. Ramachandran, S. Pitre, H. C. Brown, J. Org.Chem. 2002, 67, 5315-5319.</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>QKLCQKPAECHXCQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)C(C)=O</t>
+  </si>
+  <si>
+    <t>XXRCUYVCPSWGCC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)CCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>BRUOEHVDTAORQY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)CCC(C)=O</t>
+  </si>
+  <si>
+    <t>GMEONFUTDYJSNV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCOC(=O)CCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>XBYIXIAOQPIYHO-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)C(Cl)Cl</t>
+  </si>
+  <si>
+    <t>CERJZAHSUZVMCH-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>P. V. Ramachandran, B. Gong, A. V. Teodorovic, J Fluor Chem. 2007, 128, 844-850.</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)C(Cl)(Cl)Cl</t>
+  </si>
+  <si>
+    <t>OAMHTTBNEJBIKA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)CCl</t>
+  </si>
+  <si>
+    <t>BULLHNJGPPOUOX-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C(Cl)Cl</t>
+  </si>
+  <si>
+    <t>CSVFWMMPUJDVKH-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C(Cl)(Cl)Cl</t>
+  </si>
+  <si>
+    <t>SMZHKGXSEAGRTI-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(CF)c1ccccc1</t>
@@ -193,235 +730,28 @@
     <t>YOMBUJAFGMOIGS-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>P. V. Ramachandran, B. Gong, A. V. Teodorovic, J Fluor Chem. 2007, 128, 844-850.</t>
-  </si>
-  <si>
-    <t>O=C1CCc2ccccc21</t>
-  </si>
-  <si>
-    <t>QNXSIUBBGPHDDE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCC#CC(=O)C(CC)(CC)CCC</t>
-  </si>
-  <si>
-    <t>ZKJADHMQUMUECR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)(C)C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>OECPUBRNDKXFDX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1c(Cl)cc(Cl)cc1C(C)=O</t>
-  </si>
-  <si>
-    <t>MLXBLQUBVDCARQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(=O)C(C)C(C)=O</t>
-  </si>
-  <si>
-    <t>FNENWZWNOPCZGK-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(C#Cc1ccccc1)C(F)(F)C(F)(F)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>JLQHDTDAQBOUBB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCCC1(c1ccccc1)c1ccccc1</t>
-  </si>
-  <si>
-    <t>CBOPQVXWIKRPKD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>D. Potin, F Dumas, J D'Angelo, J. Am. Chem. Soc. 1990, 112, 3483.</t>
-  </si>
-  <si>
-    <t>COc1ccccc1C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>CSUUDNFYSFENAE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Shieh, Wen-Chung, William R. Cantrell Jr, and John A. Carlson. Tetrahedron letters, 1995, 36, 3797-3800.</t>
-  </si>
-  <si>
-    <t>COCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>YRNDGUSDBCARGC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CBr)c1ccccc1</t>
-  </si>
-  <si>
-    <t>LIGACIXOYTUXAW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COC(=O)c1ccccc1C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>NQSMEZJWJJVYOI-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)CCl</t>
-  </si>
-  <si>
-    <t>BULLHNJGPPOUOX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccc1Br</t>
-  </si>
-  <si>
-    <t>PIMNFNXBTGPCIL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccccc1C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>CKGKXGQVRVAKEA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)C#CC1CCCCC1</t>
-  </si>
-  <si>
-    <t>SCDHTAAYEHJTGD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCC(=O)c1ccc(Cl)cc1-c1ccc(Br)cc1</t>
-  </si>
-  <si>
-    <t>JGUYBMKIKPABSY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(C#Cc1ccccc1)C(F)(F)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>VCARCPYEXCPAJO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(=O)CCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>BRUOEHVDTAORQY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>P. V. Ramachandran, S. Pitre, H. C. Brown, J. Org.Chem. 2002, 67, 5315-5319.</t>
-  </si>
-  <si>
-    <t>COC(=O)[C@]1(C)CCCC1=O</t>
-  </si>
-  <si>
-    <t>TZHZMYGNHVTEFA-MRVPVSSYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCC#CC(=O)C(C)(C)C</t>
-  </si>
-  <si>
-    <t>XVKCCRCIQKVMPK-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)c1ccc(Cl)cc1</t>
-  </si>
-  <si>
-    <t>ADCYRBXQAJXJTD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1cccc2ccccc12)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>VQCWOGKZDGCRES-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(=O)C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>QKLCQKPAECHXCQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1cccc(C(C)=O)c1</t>
-  </si>
-  <si>
-    <t>BAYUSCHCCGXLAY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>M. Zhao, et al., Tetrahedron Lett. 1997, 38, 2641-2644.</t>
-  </si>
-  <si>
-    <t>CC(=O)C(C)(C)C</t>
-  </si>
-  <si>
-    <t>PJGSXYOJTGTZAV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(OC)c(C(C)=O)c1</t>
-  </si>
-  <si>
-    <t>FAXUIYJKGGUCBO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCCC12CCCC2</t>
-  </si>
-  <si>
-    <t>QRYJGVNQNLCGGZ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>C#CC(C)=O</t>
-  </si>
-  <si>
-    <t>XRGPFNGLRSIPSA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)/C=C/c1ccccc1</t>
-  </si>
-  <si>
-    <t>BWHOZHOGCMHOBV-BQYQJAHWSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C(C)C</t>
-  </si>
-  <si>
-    <t>SYBYTAAJFKOIEJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC1(C)CCCCC1=O</t>
-  </si>
-  <si>
-    <t>KNSPBSQWRKKAPI-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C(Cl)(Cl)Cl</t>
-  </si>
-  <si>
-    <t>OAMHTTBNEJBIKA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1ccccc1Cl</t>
-  </si>
-  <si>
-    <t>VMHYWKBKHMYRNF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)(C)C(=O)C#CC1CCCCC1</t>
-  </si>
-  <si>
-    <t>MSRORZBOBVAASL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCCc2ccccc21</t>
-  </si>
-  <si>
-    <t>XHLHPRDBBAGVEG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC1(C)CCCC1=O</t>
-  </si>
-  <si>
-    <t>FTGZMZBYOHMEPS-UHFFFAOYSA-N</t>
+    <t>O=C(c1ccccc1)C(F)F</t>
+  </si>
+  <si>
+    <t>OLYKCPDTXVZOQF-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>KZJRKRQSDZGHEC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)CF</t>
+  </si>
+  <si>
+    <t>MSWVMWGCNZQPIA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C(F)F</t>
+  </si>
+  <si>
+    <t>XHILZHAQBOLGFD-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CC(=O)C(F)(F)F</t>
@@ -430,307 +760,13 @@
     <t>FHUDAMLDXFJHJE-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>CCCCC#CC(=O)C(F)F</t>
-  </si>
-  <si>
-    <t>CDGZCBOPYKCCLD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCC(=O)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>NDQOKFMZSIKVBG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(C(C)=O)cc1OC</t>
-  </si>
-  <si>
-    <t>IQZLUWLMQNGTIW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(F)cc1C(C)=O</t>
-  </si>
-  <si>
-    <t>CNVGMLMIQIPAFY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC(=O)c1ccccc1C(=O)OC</t>
-  </si>
-  <si>
-    <t>QTUYJWKFWYJIOM-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C1CCCC1</t>
-  </si>
-  <si>
-    <t>LKENTYLPIUIMFG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(=O)CCC(C)=O</t>
-  </si>
-  <si>
-    <t>GMEONFUTDYJSNV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(C)=O</t>
-  </si>
-  <si>
-    <t>ZWEHNKRNPOVVGH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>FFSAXUULYPJSKH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccc2ccccc2c1)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>JWQLBVFFLIHXHA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCC#CC(=O)C(C)(CC)CCC</t>
-  </si>
-  <si>
-    <t>MMUXSGDQWCOFKS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C#Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>UPEUQDJSUFHFQP-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C(Cl)Cl</t>
-  </si>
-  <si>
-    <t>CSVFWMMPUJDVKH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>C=CCC(C)(C)C(=O)C#CCCCCCCCC</t>
-  </si>
-  <si>
-    <t>TYGJBMAZCWFZFC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCC(=O)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>OQHGRUHRHLFMBX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C(Cl)Cl</t>
-  </si>
-  <si>
-    <t>CERJZAHSUZVMCH-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C(F)F</t>
-  </si>
-  <si>
-    <t>XHILZHAQBOLGFD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(=O)CCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>XBYIXIAOQPIYHO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(C1CCCCC1)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>RPTSLLGEWZGTHJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc2ccccc2c1</t>
-  </si>
-  <si>
-    <t>XSAYZAUNJMRRIR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCCCl)c1ccc(F)cc1</t>
-  </si>
-  <si>
-    <t>HXAOUYGZEOZTJO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>P. V. Ramachandran, B Gong, H. C. Brown, Tetrahedron Asymm. 1993, 4, 2399-2400.</t>
-  </si>
-  <si>
-    <t>COc1ccc(C)cc1C(C)=O</t>
-  </si>
-  <si>
-    <t>FHIOYMGCAXTUGF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(C(C)=O)cc1</t>
-  </si>
-  <si>
-    <t>NTPLXRHDUXRPNE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCC(C)=O</t>
-  </si>
-  <si>
-    <t>ZPVFWPFBNIEHGJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC#CC(=O)C(F)(F)C(F)(F)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>DPQDBEUDQJLCFS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C(F)(F)C(F)(F)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>UKYZDGAVBNKBPQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)C#Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>XAJIQJSLJKBJTP-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>KWOLFJPFCHCOCG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>KZJRKRQSDZGHEC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(=O)C(C)(C)C(C)=O</t>
-  </si>
-  <si>
-    <t>NVAHZHOCRQCUBY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC#CC(=O)CF</t>
-  </si>
-  <si>
-    <t>RRJHAIWETICRET-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCl)c1ccc(Cl)cc1Cl</t>
-  </si>
-  <si>
-    <t>VYWPPRLJNVHPEU-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1cccs1</t>
-  </si>
-  <si>
-    <t>WYJOVVXUZNRJQY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C(F)F</t>
-  </si>
-  <si>
-    <t>OLYKCPDTXVZOQF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>KRIOVPPHQSLHCZ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(Br)cc1</t>
-  </si>
-  <si>
-    <t>WYECURVXVYPVAT-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)c1ccc([N+](=O)[O-])cc1</t>
-  </si>
-  <si>
-    <t>QHTSEJJUUBOESF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COC(=O)C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>YLHXLHGIAMFFBU-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>BSMGLVDZZMBWQB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>AMHOPTNGSNYSBL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccccc1C(C)=O</t>
-  </si>
-  <si>
-    <t>DWPLEOPKBWNPQV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C(Cl)(Cl)Cl</t>
-  </si>
-  <si>
-    <t>SMZHKGXSEAGRTI-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1c2ccccc2cc2ccccc12)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>MNCMBBIFTVWHIP-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCOC(=O)C(C)=O</t>
-  </si>
-  <si>
-    <t>XXRCUYVCPSWGCC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1C=CCCC1</t>
-  </si>
-  <si>
-    <t>FWFSEYBSWVRWGL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCl)c1ccccc1</t>
-  </si>
-  <si>
-    <t>IMACFCSSMIZSPP-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCC(=O)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>UYMHLXHLPQIDMA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)c1ccccc1F</t>
-  </si>
-  <si>
-    <t>DWFDQVMFSLLMPE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)CF</t>
-  </si>
-  <si>
-    <t>MSWVMWGCNZQPIA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCCl)c1ccc(Br)cc1</t>
-  </si>
-  <si>
-    <t>SYWQQEVHZPPLNQ-UHFFFAOYSA-N</t>
+    <t>CC(=O)c1cccc(F)c1Br</t>
+  </si>
+  <si>
+    <t>WBMUEFOEEVGDNQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Huang, Jian, et al. "Asymmetric Synthesis of Chiral Spiroketal Bisphosphine Ligands and Their Application in Enantioselective Olefin Hydrogenation." The Journal of Organic Chemistry 83.20 (2018): 12838-12846.</t>
   </si>
 </sst>
 </file>
@@ -4836,6 +4872,196 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1219200" y="134473950"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 108" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="135740775"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 109" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="137007600"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="Picture 110" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId110"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="138274425"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 111" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId111"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="139541250"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 112" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId112"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="140808075"/>
           <a:ext cx="952500" cy="952500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5133,7 +5359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
@@ -5170,7 +5396,7 @@
     </row>
     <row r="2" spans="1:9" ht="100" customHeight="1">
       <c r="A2">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -5182,10 +5408,10 @@
         <v>248</v>
       </c>
       <c r="F2">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="G2">
-        <v>-1.920691153523556</v>
+        <v>0.03950267709104377</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -5196,7 +5422,7 @@
     </row>
     <row r="3" spans="1:9" ht="100" customHeight="1">
       <c r="A3">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -5208,13 +5434,13 @@
         <v>248</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>53.5</v>
       </c>
       <c r="G3">
-        <v>-0.2001051401535412</v>
+        <v>-0.06920598452264508</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5222,25 +5448,25 @@
     </row>
     <row r="4" spans="1:9" ht="100" customHeight="1">
       <c r="A4">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
       </c>
       <c r="E4">
         <v>248</v>
       </c>
       <c r="F4">
-        <v>1.5</v>
+        <v>1.299999999999997</v>
       </c>
       <c r="G4">
-        <v>2.065179567503287</v>
+        <v>2.136803750966795</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5248,25 +5474,25 @@
     </row>
     <row r="5" spans="1:9" ht="100" customHeight="1">
       <c r="A5">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1.350000000000001</v>
       </c>
       <c r="G5">
-        <v>1.884649482472939</v>
+        <v>2.117928070821824</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5274,25 +5500,25 @@
     </row>
     <row r="6" spans="1:9" ht="100" customHeight="1">
       <c r="A6">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>248</v>
       </c>
       <c r="F6">
-        <v>98.5</v>
+        <v>0.8999999999999986</v>
       </c>
       <c r="G6">
-        <v>-2.065179567503288</v>
+        <v>2.320279323575566</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5300,25 +5526,25 @@
     </row>
     <row r="7" spans="1:9" ht="100" customHeight="1">
       <c r="A7">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>248</v>
       </c>
       <c r="F7">
-        <v>99.5</v>
+        <v>2.5</v>
       </c>
       <c r="G7">
-        <v>-2.61235179709804</v>
+        <v>1.808040943597903</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5326,25 +5552,25 @@
     </row>
     <row r="8" spans="1:9" ht="100" customHeight="1">
       <c r="A8">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F8">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>3.139035627158119</v>
+        <v>1.453139524998222</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5352,25 +5578,25 @@
     </row>
     <row r="9" spans="1:9" ht="100" customHeight="1">
       <c r="A9">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="G9">
-        <v>2.307927273185564</v>
+        <v>-1.06547349528128</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5378,25 +5604,25 @@
     </row>
     <row r="10" spans="1:9" ht="100" customHeight="1">
       <c r="A10">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E10">
         <v>248</v>
       </c>
       <c r="F10">
-        <v>76.5</v>
+        <v>1.299999999999997</v>
       </c>
       <c r="G10">
-        <v>-0.5824968785696466</v>
+        <v>2.136803750966795</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -5404,25 +5630,25 @@
     </row>
     <row r="11" spans="1:9" ht="100" customHeight="1">
       <c r="A11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>248</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>6.299999999999997</v>
       </c>
       <c r="G11">
-        <v>1.808040943597903</v>
+        <v>1.332281203281557</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -5430,25 +5656,25 @@
     </row>
     <row r="12" spans="1:9" ht="100" customHeight="1">
       <c r="A12">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>248</v>
       </c>
       <c r="F12">
-        <v>99.5</v>
+        <v>0.9500000000000028</v>
       </c>
       <c r="G12">
-        <v>-2.61235179709804</v>
+        <v>2.293347004688446</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -5456,25 +5682,25 @@
     </row>
     <row r="13" spans="1:9" ht="100" customHeight="1">
       <c r="A13">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E13">
         <v>248</v>
       </c>
       <c r="F13">
-        <v>1.5</v>
+        <v>3.799999999999997</v>
       </c>
       <c r="G13">
-        <v>2.065179567503287</v>
+        <v>1.594774490144374</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -5482,25 +5708,25 @@
     </row>
     <row r="14" spans="1:9" ht="100" customHeight="1">
       <c r="A14">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E14">
         <v>248</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>4.350000000000001</v>
       </c>
       <c r="G14">
-        <v>2.267783548438423</v>
+        <v>1.525233356759743</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -5508,25 +5734,25 @@
     </row>
     <row r="15" spans="1:9" ht="100" customHeight="1">
       <c r="A15">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E15">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F15">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G15">
-        <v>0.2001051401535413</v>
+        <v>1.448360638914646</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -5534,25 +5760,25 @@
     </row>
     <row r="16" spans="1:9" ht="100" customHeight="1">
       <c r="A16">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E16">
         <v>248</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G16">
-        <v>1.920691153523556</v>
+        <v>-1.276582925099217</v>
       </c>
       <c r="H16" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -5560,25 +5786,25 @@
     </row>
     <row r="17" spans="1:9" ht="100" customHeight="1">
       <c r="A17">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E17">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F17">
-        <v>64</v>
+        <v>1.5</v>
       </c>
       <c r="G17">
-        <v>-0.3412024452107102</v>
+        <v>2.065179567503287</v>
       </c>
       <c r="H17" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -5586,25 +5812,25 @@
     </row>
     <row r="18" spans="1:9" ht="100" customHeight="1">
       <c r="A18">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E18">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F18">
-        <v>31</v>
+        <v>1.5</v>
       </c>
       <c r="G18">
-        <v>0.4744867473524853</v>
+        <v>2.065179567503287</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -5612,13 +5838,13 @@
     </row>
     <row r="19" spans="1:9" ht="100" customHeight="1">
       <c r="A19">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E19">
         <v>248</v>
@@ -5630,7 +5856,7 @@
         <v>2.267783548438423</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -5638,25 +5864,25 @@
     </row>
     <row r="20" spans="1:9" ht="100" customHeight="1">
       <c r="A20">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E20">
         <v>248</v>
       </c>
       <c r="F20">
-        <v>37</v>
+        <v>96.5</v>
       </c>
       <c r="G20">
-        <v>0.2626596419205716</v>
+        <v>-1.636897285266562</v>
       </c>
       <c r="H20" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -5664,25 +5890,25 @@
     </row>
     <row r="21" spans="1:9" ht="100" customHeight="1">
       <c r="A21">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E21">
         <v>248</v>
       </c>
       <c r="F21">
-        <v>97.5</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>-1.808040943597905</v>
+        <v>2.267783548438423</v>
       </c>
       <c r="H21" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5690,25 +5916,25 @@
     </row>
     <row r="22" spans="1:9" ht="100" customHeight="1">
       <c r="A22">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E22">
         <v>248</v>
       </c>
       <c r="F22">
-        <v>1.299999999999997</v>
+        <v>37</v>
       </c>
       <c r="G22">
-        <v>2.136803750966795</v>
+        <v>0.2626596419205716</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -5716,25 +5942,25 @@
     </row>
     <row r="23" spans="1:9" ht="100" customHeight="1">
       <c r="A23">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E23">
         <v>248</v>
       </c>
       <c r="F23">
-        <v>99.5</v>
+        <v>38.5</v>
       </c>
       <c r="G23">
-        <v>-2.61235179709804</v>
+        <v>0.2311543712701654</v>
       </c>
       <c r="H23" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5742,25 +5968,25 @@
     </row>
     <row r="24" spans="1:9" ht="100" customHeight="1">
       <c r="A24">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E24">
         <v>248</v>
       </c>
       <c r="F24">
-        <v>89.65000000000001</v>
+        <v>31</v>
       </c>
       <c r="G24">
-        <v>-1.06547349528128</v>
+        <v>0.3948748769913301</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5768,25 +5994,25 @@
     </row>
     <row r="25" spans="1:9" ht="100" customHeight="1">
       <c r="A25">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E25">
         <v>248</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>27.5</v>
       </c>
       <c r="G25">
-        <v>1.715524225407504</v>
+        <v>0.4784185629834729</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5794,25 +6020,25 @@
     </row>
     <row r="26" spans="1:9" ht="100" customHeight="1">
       <c r="A26">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E26">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>1.448360638914646</v>
+        <v>2.269203661219363</v>
       </c>
       <c r="H26" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5820,25 +6046,25 @@
     </row>
     <row r="27" spans="1:9" ht="100" customHeight="1">
       <c r="A27">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E27">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>97.5</v>
       </c>
       <c r="G27">
-        <v>2.061396045046114</v>
+        <v>-1.808040943597905</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5846,25 +6072,25 @@
     </row>
     <row r="28" spans="1:9" ht="100" customHeight="1">
       <c r="A28">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E28">
-        <v>293</v>
+        <v>248</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G28">
-        <v>2.269203661219363</v>
+        <v>2.065179567503287</v>
       </c>
       <c r="H28" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5872,25 +6098,25 @@
     </row>
     <row r="29" spans="1:9" ht="100" customHeight="1">
       <c r="A29">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E29">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F29">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2.612351797098031</v>
       </c>
       <c r="H29" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5898,25 +6124,25 @@
     </row>
     <row r="30" spans="1:9" ht="100" customHeight="1">
       <c r="A30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E30">
         <v>248</v>
       </c>
       <c r="F30">
-        <v>97.5</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>-1.808040943597905</v>
+        <v>2.267783548438423</v>
       </c>
       <c r="H30" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5924,25 +6150,25 @@
     </row>
     <row r="31" spans="1:9" ht="100" customHeight="1">
       <c r="A31">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E31">
         <v>248</v>
       </c>
       <c r="F31">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>-1.276582925099217</v>
+        <v>1.920691153523556</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5950,25 +6176,25 @@
     </row>
     <row r="32" spans="1:9" ht="100" customHeight="1">
       <c r="A32">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E32">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F32">
+        <v>2.5</v>
+      </c>
+      <c r="G32">
+        <v>1.808040943597903</v>
+      </c>
+      <c r="H32" t="s">
         <v>65</v>
-      </c>
-      <c r="G32">
-        <v>-0.3671026313690585</v>
-      </c>
-      <c r="H32" t="s">
-        <v>41</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5976,25 +6202,25 @@
     </row>
     <row r="33" spans="1:9" ht="100" customHeight="1">
       <c r="A33">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E33">
         <v>248</v>
       </c>
       <c r="F33">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="G33">
-        <v>-0.1796241929564407</v>
+        <v>1.141825110249225</v>
       </c>
       <c r="H33" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -6002,25 +6228,25 @@
     </row>
     <row r="34" spans="1:9" ht="100" customHeight="1">
       <c r="A34">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E34">
         <v>248</v>
       </c>
       <c r="F34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>2.612351797098031</v>
+        <v>2.267783548438423</v>
       </c>
       <c r="H34" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -6028,25 +6254,25 @@
     </row>
     <row r="35" spans="1:9" ht="100" customHeight="1">
       <c r="A35">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E35">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F35">
-        <v>50</v>
+        <v>3.5</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1.636897285266561</v>
       </c>
       <c r="H35" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6054,25 +6280,25 @@
     </row>
     <row r="36" spans="1:9" ht="100" customHeight="1">
       <c r="A36">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E36">
         <v>248</v>
       </c>
       <c r="F36">
-        <v>69.5</v>
+        <v>4.5</v>
       </c>
       <c r="G36">
-        <v>-0.4064631060318465</v>
+        <v>1.507727708802602</v>
       </c>
       <c r="H36" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -6080,25 +6306,25 @@
     </row>
     <row r="37" spans="1:9" ht="100" customHeight="1">
       <c r="A37">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E37">
         <v>248</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G37">
-        <v>2.267783548438423</v>
+        <v>1.808040943597903</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6106,25 +6332,25 @@
     </row>
     <row r="38" spans="1:9" ht="100" customHeight="1">
       <c r="A38">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E38">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="G38">
-        <v>2.307927273185564</v>
+        <v>-2.26778354843842</v>
       </c>
       <c r="H38" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -6132,25 +6358,25 @@
     </row>
     <row r="39" spans="1:9" ht="100" customHeight="1">
       <c r="A39">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E39">
         <v>248</v>
       </c>
       <c r="F39">
-        <v>0.5</v>
+        <v>98.5</v>
       </c>
       <c r="G39">
-        <v>2.612351797098031</v>
+        <v>-2.065179567503288</v>
       </c>
       <c r="H39" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -6158,25 +6384,25 @@
     </row>
     <row r="40" spans="1:9" ht="100" customHeight="1">
       <c r="A40">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E40">
         <v>248</v>
       </c>
       <c r="F40">
-        <v>3.5</v>
+        <v>98</v>
       </c>
       <c r="G40">
-        <v>1.636897285266561</v>
+        <v>-1.920691153523556</v>
       </c>
       <c r="H40" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -6184,25 +6410,25 @@
     </row>
     <row r="41" spans="1:9" ht="100" customHeight="1">
       <c r="A41">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E41">
         <v>248</v>
       </c>
       <c r="F41">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="G41">
-        <v>-2.26778354843842</v>
+        <v>-2.61235179709804</v>
       </c>
       <c r="H41" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -6210,25 +6436,25 @@
     </row>
     <row r="42" spans="1:9" ht="100" customHeight="1">
       <c r="A42">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D42" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E42">
         <v>248</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>99.5</v>
       </c>
       <c r="G42">
-        <v>2.267783548438423</v>
+        <v>-2.61235179709804</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -6236,25 +6462,25 @@
     </row>
     <row r="43" spans="1:9" ht="100" customHeight="1">
       <c r="A43">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E43">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F43">
-        <v>11</v>
+        <v>99.5</v>
       </c>
       <c r="G43">
-        <v>1.239851285303664</v>
+        <v>-2.61235179709804</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -6262,25 +6488,25 @@
     </row>
     <row r="44" spans="1:9" ht="100" customHeight="1">
       <c r="A44">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D44" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E44">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="F44">
-        <v>94.5</v>
+        <v>34</v>
       </c>
       <c r="G44">
-        <v>-1.103556668584487</v>
+        <v>0.3273489621763137</v>
       </c>
       <c r="H44" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -6288,25 +6514,25 @@
     </row>
     <row r="45" spans="1:9" ht="100" customHeight="1">
       <c r="A45">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E45">
         <v>248</v>
       </c>
       <c r="F45">
-        <v>2.5</v>
+        <v>97.5</v>
       </c>
       <c r="G45">
-        <v>1.808040943597903</v>
+        <v>-1.808040943597905</v>
       </c>
       <c r="H45" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -6314,25 +6540,25 @@
     </row>
     <row r="46" spans="1:9" ht="100" customHeight="1">
       <c r="A46">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E46">
         <v>248</v>
       </c>
       <c r="F46">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="G46">
-        <v>1.808040943597903</v>
+        <v>1.112422729872089</v>
       </c>
       <c r="H46" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -6340,25 +6566,25 @@
     </row>
     <row r="47" spans="1:9" ht="100" customHeight="1">
       <c r="A47">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E47">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="F47">
-        <v>3.5</v>
+        <v>32</v>
       </c>
       <c r="G47">
-        <v>1.801907092249077</v>
+        <v>0.3720014599087912</v>
       </c>
       <c r="H47" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -6366,25 +6592,25 @@
     </row>
     <row r="48" spans="1:9" ht="100" customHeight="1">
       <c r="A48">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E48">
         <v>248</v>
       </c>
       <c r="F48">
-        <v>2.5</v>
+        <v>60.5</v>
       </c>
       <c r="G48">
-        <v>1.808040943597903</v>
+        <v>-0.2104086459133792</v>
       </c>
       <c r="H48" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -6395,10 +6621,10 @@
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E49">
         <v>248</v>
@@ -6410,7 +6636,7 @@
         <v>-0.1694418635416117</v>
       </c>
       <c r="H49" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -6418,25 +6644,25 @@
     </row>
     <row r="50" spans="1:9" ht="100" customHeight="1">
       <c r="A50">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E50">
         <v>248</v>
       </c>
       <c r="F50">
-        <v>9.5</v>
+        <v>64</v>
       </c>
       <c r="G50">
-        <v>1.112422729872089</v>
+        <v>-0.2839537127928058</v>
       </c>
       <c r="H50" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -6444,25 +6670,25 @@
     </row>
     <row r="51" spans="1:9" ht="100" customHeight="1">
       <c r="A51">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E51">
         <v>248</v>
       </c>
       <c r="F51">
-        <v>34</v>
+        <v>76.5</v>
       </c>
       <c r="G51">
-        <v>0.3273489621763137</v>
+        <v>-0.5824968785696466</v>
       </c>
       <c r="H51" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -6470,25 +6696,25 @@
     </row>
     <row r="52" spans="1:9" ht="100" customHeight="1">
       <c r="A52">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D52" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E52">
         <v>248</v>
       </c>
       <c r="F52">
-        <v>4.5</v>
+        <v>69.5</v>
       </c>
       <c r="G52">
-        <v>1.507727708802602</v>
+        <v>-0.4064631060318465</v>
       </c>
       <c r="H52" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -6496,25 +6722,25 @@
     </row>
     <row r="53" spans="1:9" ht="100" customHeight="1">
       <c r="A53">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" t="s">
         <v>118</v>
       </c>
-      <c r="B53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" t="s">
-        <v>127</v>
-      </c>
       <c r="E53">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="F53">
-        <v>4.5</v>
+        <v>98.5</v>
       </c>
       <c r="G53">
-        <v>1.507727708802602</v>
+        <v>-2.464891741858764</v>
       </c>
       <c r="H53" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -6522,25 +6748,25 @@
     </row>
     <row r="54" spans="1:9" ht="100" customHeight="1">
       <c r="A54">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E54">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F54">
-        <v>57.5</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>-0.1792586026380871</v>
+        <v>2.267783548438423</v>
       </c>
       <c r="H54" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -6548,25 +6774,25 @@
     </row>
     <row r="55" spans="1:9" ht="100" customHeight="1">
       <c r="A55">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E55">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F55">
-        <v>98.5</v>
+        <v>11</v>
       </c>
       <c r="G55">
-        <v>-2.464891741858764</v>
+        <v>1.239851285303664</v>
       </c>
       <c r="H55" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -6574,25 +6800,25 @@
     </row>
     <row r="56" spans="1:9" ht="100" customHeight="1">
       <c r="A56">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E56">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F56">
-        <v>6.299999999999997</v>
+        <v>4.5</v>
       </c>
       <c r="G56">
-        <v>1.332281203281557</v>
+        <v>1.811705069448287</v>
       </c>
       <c r="H56" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -6600,25 +6826,25 @@
     </row>
     <row r="57" spans="1:9" ht="100" customHeight="1">
       <c r="A57">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D57" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E57">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G57">
-        <v>2.267783548438423</v>
+        <v>1.372031785702698</v>
       </c>
       <c r="H57" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -6626,25 +6852,25 @@
     </row>
     <row r="58" spans="1:9" ht="100" customHeight="1">
       <c r="A58">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D58" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E58">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>2.269203661219363</v>
+        <v>1.884649482472939</v>
       </c>
       <c r="H58" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -6652,25 +6878,25 @@
     </row>
     <row r="59" spans="1:9" ht="100" customHeight="1">
       <c r="A59">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D59" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E59">
         <v>298</v>
       </c>
       <c r="F59">
-        <v>42.5</v>
+        <v>6.5</v>
       </c>
       <c r="G59">
-        <v>0.1792586026380871</v>
+        <v>1.581085764005266</v>
       </c>
       <c r="H59" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6681,10 +6907,10 @@
         <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D60" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E60">
         <v>298</v>
@@ -6696,7 +6922,7 @@
         <v>1.884649482472939</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -6704,25 +6930,25 @@
     </row>
     <row r="61" spans="1:9" ht="100" customHeight="1">
       <c r="A61">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E61">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="G61">
-        <v>1.715524225407504</v>
+        <v>1.811705069448287</v>
       </c>
       <c r="H61" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6730,25 +6956,25 @@
     </row>
     <row r="62" spans="1:9" ht="100" customHeight="1">
       <c r="A62">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E62">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="G62">
-        <v>1.715524225407504</v>
+        <v>1.581085764005266</v>
       </c>
       <c r="H62" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -6756,25 +6982,25 @@
     </row>
     <row r="63" spans="1:9" ht="100" customHeight="1">
       <c r="A63">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D63" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E63">
         <v>248</v>
       </c>
       <c r="F63">
-        <v>0.5</v>
+        <v>99.5</v>
       </c>
       <c r="G63">
-        <v>2.612351797098031</v>
+        <v>-2.61235179709804</v>
       </c>
       <c r="H63" t="s">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -6782,25 +7008,25 @@
     </row>
     <row r="64" spans="1:9" ht="100" customHeight="1">
       <c r="A64">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D64" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E64">
         <v>248</v>
       </c>
       <c r="F64">
-        <v>27.5</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>0.4784185629834729</v>
+        <v>2.267783548438423</v>
       </c>
       <c r="H64" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6808,25 +7034,25 @@
     </row>
     <row r="65" spans="1:9" ht="100" customHeight="1">
       <c r="A65">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D65" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E65">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F65">
-        <v>63.5</v>
+        <v>64</v>
       </c>
       <c r="G65">
-        <v>-0.2732756675134899</v>
+        <v>-0.3412024452107102</v>
       </c>
       <c r="H65" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6834,25 +7060,25 @@
     </row>
     <row r="66" spans="1:9" ht="100" customHeight="1">
       <c r="A66">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E66">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F66">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G66">
-        <v>0.03950267709104377</v>
+        <v>0.4744867473524853</v>
       </c>
       <c r="H66" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -6860,25 +7086,25 @@
     </row>
     <row r="67" spans="1:9" ht="100" customHeight="1">
       <c r="A67">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E67">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F67">
-        <v>0.8999999999999986</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>2.320279323575566</v>
+        <v>2.307927273185564</v>
       </c>
       <c r="H67" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -6886,25 +7112,25 @@
     </row>
     <row r="68" spans="1:9" ht="100" customHeight="1">
       <c r="A68">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D68" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E68">
         <v>298</v>
       </c>
       <c r="F68">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>1.811705069448287</v>
+        <v>2.061396045046114</v>
       </c>
       <c r="H68" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -6912,25 +7138,25 @@
     </row>
     <row r="69" spans="1:9" ht="100" customHeight="1">
       <c r="A69">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D69" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E69">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F69">
-        <v>99.5</v>
+        <v>73</v>
       </c>
       <c r="G69">
-        <v>-2.61235179709804</v>
+        <v>-0.5898310795119318</v>
       </c>
       <c r="H69" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -6938,25 +7164,25 @@
     </row>
     <row r="70" spans="1:9" ht="100" customHeight="1">
       <c r="A70">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D70" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E70">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F70">
-        <v>60.5</v>
+        <v>42.5</v>
       </c>
       <c r="G70">
-        <v>-0.2104086459133792</v>
+        <v>0.1792586026380871</v>
       </c>
       <c r="H70" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -6964,25 +7190,25 @@
     </row>
     <row r="71" spans="1:9" ht="100" customHeight="1">
       <c r="A71">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D71" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E71">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F71">
-        <v>57.5</v>
+        <v>0.5</v>
       </c>
       <c r="G71">
-        <v>-0.1491816558867302</v>
+        <v>3.139035627158119</v>
       </c>
       <c r="H71" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -6990,25 +7216,25 @@
     </row>
     <row r="72" spans="1:9" ht="100" customHeight="1">
       <c r="A72">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D72" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E72">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F72">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="G72">
-        <v>-1.920691153523556</v>
+        <v>2.307927273185564</v>
       </c>
       <c r="H72" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -7016,25 +7242,25 @@
     </row>
     <row r="73" spans="1:9" ht="100" customHeight="1">
       <c r="A73">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B73" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E73">
         <v>298</v>
       </c>
       <c r="F73">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G73">
-        <v>1.811705069448287</v>
+        <v>1.884649482472939</v>
       </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -7042,25 +7268,25 @@
     </row>
     <row r="74" spans="1:9" ht="100" customHeight="1">
       <c r="A74">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D74" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E74">
         <v>248</v>
       </c>
       <c r="F74">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="G74">
-        <v>-1.141825110249225</v>
+        <v>-0.4181584400582927</v>
       </c>
       <c r="H74" t="s">
-        <v>59</v>
+        <v>164</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -7068,25 +7294,25 @@
     </row>
     <row r="75" spans="1:9" ht="100" customHeight="1">
       <c r="A75">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E75">
         <v>248</v>
       </c>
       <c r="F75">
-        <v>52.5</v>
+        <v>34</v>
       </c>
       <c r="G75">
-        <v>-0.04939318846704208</v>
+        <v>0.3273489621763137</v>
       </c>
       <c r="H75" t="s">
-        <v>59</v>
+        <v>164</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -7094,25 +7320,25 @@
     </row>
     <row r="76" spans="1:9" ht="100" customHeight="1">
       <c r="A76">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D76" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E76">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="G76">
-        <v>2.267783548438423</v>
+        <v>1.811705069448287</v>
       </c>
       <c r="H76" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -7120,25 +7346,25 @@
     </row>
     <row r="77" spans="1:9" ht="100" customHeight="1">
       <c r="A77">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E77">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F77">
-        <v>6.5</v>
+        <v>40</v>
       </c>
       <c r="G77">
-        <v>1.581085764005266</v>
+        <v>0.2001051401535413</v>
       </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -7146,25 +7372,25 @@
     </row>
     <row r="78" spans="1:9" ht="100" customHeight="1">
       <c r="A78">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E78">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="F78">
-        <v>0.9500000000000028</v>
+        <v>3.5</v>
       </c>
       <c r="G78">
-        <v>2.293347004688446</v>
+        <v>1.801907092249077</v>
       </c>
       <c r="H78" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -7172,25 +7398,25 @@
     </row>
     <row r="79" spans="1:9" ht="100" customHeight="1">
       <c r="A79">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E79">
         <v>248</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G79">
-        <v>2.267783548438423</v>
+        <v>1.808040943597903</v>
       </c>
       <c r="H79" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -7198,25 +7424,25 @@
     </row>
     <row r="80" spans="1:9" ht="100" customHeight="1">
       <c r="A80">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B80" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D80" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E80">
         <v>248</v>
       </c>
       <c r="F80">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>1.808040943597903</v>
+        <v>1.715524225407504</v>
       </c>
       <c r="H80" t="s">
-        <v>14</v>
+        <v>171</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -7224,25 +7450,25 @@
     </row>
     <row r="81" spans="1:9" ht="100" customHeight="1">
       <c r="A81">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D81" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E81">
         <v>248</v>
       </c>
       <c r="F81">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="G81">
-        <v>1.315802917695658</v>
+        <v>1.715524225407504</v>
       </c>
       <c r="H81" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -7250,25 +7476,25 @@
     </row>
     <row r="82" spans="1:9" ht="100" customHeight="1">
       <c r="A82">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="B82" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D82" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E82">
         <v>248</v>
       </c>
       <c r="F82">
-        <v>53.5</v>
+        <v>40</v>
       </c>
       <c r="G82">
-        <v>-0.06920598452264508</v>
+        <v>0.2001051401535413</v>
       </c>
       <c r="H82" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -7276,25 +7502,25 @@
     </row>
     <row r="83" spans="1:9" ht="100" customHeight="1">
       <c r="A83">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D83" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E83">
         <v>298</v>
       </c>
       <c r="F83">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G83">
-        <v>1.884649482472939</v>
+        <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -7302,25 +7528,25 @@
     </row>
     <row r="84" spans="1:9" ht="100" customHeight="1">
       <c r="A84">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D84" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E84">
         <v>298</v>
       </c>
       <c r="F84">
-        <v>6.5</v>
+        <v>64</v>
       </c>
       <c r="G84">
-        <v>1.581085764005266</v>
+        <v>-0.3412024452107102</v>
       </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -7328,25 +7554,25 @@
     </row>
     <row r="85" spans="1:9" ht="100" customHeight="1">
       <c r="A85">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D85" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E85">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F85">
-        <v>64</v>
+        <v>57.5</v>
       </c>
       <c r="G85">
-        <v>-0.2839537127928058</v>
+        <v>-0.1792586026380871</v>
       </c>
       <c r="H85" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -7354,155 +7580,155 @@
     </row>
     <row r="86" spans="1:9" ht="100" customHeight="1">
       <c r="A86">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D86" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E86">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F86">
-        <v>1.299999999999997</v>
+        <v>50</v>
       </c>
       <c r="G86">
-        <v>2.136803750966795</v>
+        <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>36</v>
+        <v>184</v>
       </c>
       <c r="I86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="100" customHeight="1">
       <c r="A87">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B87" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D87" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E87">
-        <v>293</v>
+        <v>248</v>
       </c>
       <c r="F87">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="G87">
-        <v>1.716814035582576</v>
+        <v>-1.920691153523556</v>
       </c>
       <c r="H87" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="I87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="100" customHeight="1">
       <c r="A88">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="B88" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D88" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E88">
         <v>248</v>
       </c>
       <c r="F88">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="G88">
-        <v>1.141825110249225</v>
+        <v>2.065179567503287</v>
       </c>
       <c r="H88" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="I88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="100" customHeight="1">
       <c r="A89">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="B89" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D89" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E89">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F89">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>-0.5898310795119318</v>
+        <v>2.267783548438423</v>
       </c>
       <c r="H89" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="I89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="100" customHeight="1">
       <c r="A90">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="B90" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E90">
         <v>248</v>
       </c>
       <c r="F90">
-        <v>96.5</v>
+        <v>0.5</v>
       </c>
       <c r="G90">
-        <v>-1.636897285266562</v>
+        <v>2.612351797098031</v>
       </c>
       <c r="H90" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="100" customHeight="1">
       <c r="A91">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="B91" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D91" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E91">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="F91">
-        <v>4.350000000000001</v>
+        <v>65</v>
       </c>
       <c r="G91">
-        <v>1.525233356759743</v>
+        <v>-0.3671026313690585</v>
       </c>
       <c r="H91" t="s">
-        <v>36</v>
+        <v>196</v>
       </c>
       <c r="I91">
         <v>1</v>
@@ -7510,25 +7736,25 @@
     </row>
     <row r="92" spans="1:9" ht="100" customHeight="1">
       <c r="A92">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B92" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D92" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E92">
         <v>248</v>
       </c>
       <c r="F92">
-        <v>92.5</v>
+        <v>1.5</v>
       </c>
       <c r="G92">
-        <v>-1.239873071544692</v>
+        <v>2.065179567503287</v>
       </c>
       <c r="H92" t="s">
-        <v>59</v>
+        <v>205</v>
       </c>
       <c r="I92">
         <v>1</v>
@@ -7536,25 +7762,25 @@
     </row>
     <row r="93" spans="1:9" ht="100" customHeight="1">
       <c r="A93">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="B93" t="s">
+        <v>206</v>
+      </c>
+      <c r="D93" t="s">
         <v>207</v>
-      </c>
-      <c r="D93" t="s">
-        <v>208</v>
       </c>
       <c r="E93">
         <v>248</v>
       </c>
       <c r="F93">
-        <v>1.350000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="G93">
-        <v>2.117928070821824</v>
+        <v>1.808040943597903</v>
       </c>
       <c r="H93" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="I93">
         <v>1</v>
@@ -7562,25 +7788,25 @@
     </row>
     <row r="94" spans="1:9" ht="100" customHeight="1">
       <c r="A94">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="B94" t="s">
+        <v>208</v>
+      </c>
+      <c r="D94" t="s">
         <v>209</v>
-      </c>
-      <c r="D94" t="s">
-        <v>210</v>
       </c>
       <c r="E94">
         <v>248</v>
       </c>
       <c r="F94">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="G94">
-        <v>2.065179567503287</v>
+        <v>1.315802917695658</v>
       </c>
       <c r="H94" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="I94">
         <v>1</v>
@@ -7588,25 +7814,25 @@
     </row>
     <row r="95" spans="1:9" ht="100" customHeight="1">
       <c r="A95">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="B95" t="s">
+        <v>210</v>
+      </c>
+      <c r="D95" t="s">
         <v>211</v>
-      </c>
-      <c r="D95" t="s">
-        <v>212</v>
       </c>
       <c r="E95">
         <v>248</v>
       </c>
       <c r="F95">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G95">
-        <v>2.065179567503287</v>
+        <v>1.715524225407504</v>
       </c>
       <c r="H95" t="s">
-        <v>23</v>
+        <v>205</v>
       </c>
       <c r="I95">
         <v>1</v>
@@ -7614,13 +7840,13 @@
     </row>
     <row r="96" spans="1:9" ht="100" customHeight="1">
       <c r="A96">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B96" t="s">
+        <v>212</v>
+      </c>
+      <c r="D96" t="s">
         <v>213</v>
-      </c>
-      <c r="D96" t="s">
-        <v>214</v>
       </c>
       <c r="E96">
         <v>195</v>
@@ -7632,7 +7858,7 @@
         <v>-1.23324378886652</v>
       </c>
       <c r="H96" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="I96">
         <v>1</v>
@@ -7640,7 +7866,7 @@
     </row>
     <row r="97" spans="1:9" ht="100" customHeight="1">
       <c r="A97">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="B97" t="s">
         <v>215</v>
@@ -7649,16 +7875,16 @@
         <v>216</v>
       </c>
       <c r="E97">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="F97">
-        <v>5</v>
+        <v>94.5</v>
       </c>
       <c r="G97">
-        <v>1.453139524998222</v>
+        <v>-1.103556668584487</v>
       </c>
       <c r="H97" t="s">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="I97">
         <v>1</v>
@@ -7666,7 +7892,7 @@
     </row>
     <row r="98" spans="1:9" ht="100" customHeight="1">
       <c r="A98">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="B98" t="s">
         <v>217</v>
@@ -7675,16 +7901,16 @@
         <v>218</v>
       </c>
       <c r="E98">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="F98">
-        <v>38.5</v>
+        <v>9</v>
       </c>
       <c r="G98">
-        <v>0.2311543712701654</v>
+        <v>0.8978060342685438</v>
       </c>
       <c r="H98" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
       <c r="I98">
         <v>1</v>
@@ -7692,7 +7918,7 @@
     </row>
     <row r="99" spans="1:9" ht="100" customHeight="1">
       <c r="A99">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B99" t="s">
         <v>219</v>
@@ -7704,13 +7930,13 @@
         <v>248</v>
       </c>
       <c r="F99">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G99">
-        <v>2.065179567503287</v>
+        <v>2.612351797098031</v>
       </c>
       <c r="H99" t="s">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="I99">
         <v>1</v>
@@ -7718,7 +7944,7 @@
     </row>
     <row r="100" spans="1:9" ht="100" customHeight="1">
       <c r="A100">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B100" t="s">
         <v>221</v>
@@ -7727,16 +7953,16 @@
         <v>222</v>
       </c>
       <c r="E100">
-        <v>293</v>
+        <v>248</v>
       </c>
       <c r="F100">
-        <v>4.5</v>
+        <v>63.5</v>
       </c>
       <c r="G100">
-        <v>1.781307333383719</v>
+        <v>-0.2732756675134899</v>
       </c>
       <c r="H100" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -7744,7 +7970,7 @@
     </row>
     <row r="101" spans="1:9" ht="100" customHeight="1">
       <c r="A101">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="B101" t="s">
         <v>223</v>
@@ -7753,16 +7979,16 @@
         <v>224</v>
       </c>
       <c r="E101">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="F101">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>1.372031785702698</v>
+        <v>2.267783548438423</v>
       </c>
       <c r="H101" t="s">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="I101">
         <v>1</v>
@@ -7770,7 +7996,7 @@
     </row>
     <row r="102" spans="1:9" ht="100" customHeight="1">
       <c r="A102">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B102" t="s">
         <v>225</v>
@@ -7779,16 +8005,16 @@
         <v>226</v>
       </c>
       <c r="E102">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="F102">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="G102">
-        <v>0.8978060342685438</v>
+        <v>-1.141825110249225</v>
       </c>
       <c r="H102" t="s">
-        <v>98</v>
+        <v>227</v>
       </c>
       <c r="I102">
         <v>1</v>
@@ -7796,25 +8022,25 @@
     </row>
     <row r="103" spans="1:9" ht="100" customHeight="1">
       <c r="A103">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="B103" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D103" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E103">
         <v>248</v>
       </c>
       <c r="F103">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="G103">
-        <v>0.3720014599087912</v>
+        <v>1.507727708802602</v>
       </c>
       <c r="H103" t="s">
-        <v>23</v>
+        <v>227</v>
       </c>
       <c r="I103">
         <v>1</v>
@@ -7822,25 +8048,25 @@
     </row>
     <row r="104" spans="1:9" ht="100" customHeight="1">
       <c r="A104">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="B104" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D104" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E104">
         <v>248</v>
       </c>
       <c r="F104">
-        <v>97.5</v>
+        <v>59</v>
       </c>
       <c r="G104">
-        <v>-1.808040943597905</v>
+        <v>-0.1796241929564407</v>
       </c>
       <c r="H104" t="s">
-        <v>23</v>
+        <v>227</v>
       </c>
       <c r="I104">
         <v>1</v>
@@ -7848,25 +8074,25 @@
     </row>
     <row r="105" spans="1:9" ht="100" customHeight="1">
       <c r="A105">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="B105" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D105" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E105">
         <v>248</v>
       </c>
       <c r="F105">
-        <v>31</v>
+        <v>57.5</v>
       </c>
       <c r="G105">
-        <v>0.3948748769913301</v>
+        <v>-0.1491816558867302</v>
       </c>
       <c r="H105" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="I105">
         <v>1</v>
@@ -7874,25 +8100,25 @@
     </row>
     <row r="106" spans="1:9" ht="100" customHeight="1">
       <c r="A106">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B106" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D106" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E106">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F106">
-        <v>64</v>
+        <v>4.5</v>
       </c>
       <c r="G106">
-        <v>-0.3412024452107102</v>
+        <v>1.781307333383719</v>
       </c>
       <c r="H106" t="s">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="I106">
         <v>1</v>
@@ -7903,22 +8129,22 @@
         <v>125</v>
       </c>
       <c r="B107" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D107" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E107">
         <v>248</v>
       </c>
       <c r="F107">
-        <v>19.5</v>
+        <v>97.5</v>
       </c>
       <c r="G107">
-        <v>0.6997337386092292</v>
+        <v>-1.808040943597905</v>
       </c>
       <c r="H107" t="s">
-        <v>59</v>
+        <v>227</v>
       </c>
       <c r="I107">
         <v>1</v>
@@ -7926,27 +8152,157 @@
     </row>
     <row r="108" spans="1:9" ht="100" customHeight="1">
       <c r="A108">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D108" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E108">
         <v>248</v>
       </c>
       <c r="F108">
+        <v>92.5</v>
+      </c>
+      <c r="G108">
+        <v>-1.239873071544692</v>
+      </c>
+      <c r="H108" t="s">
+        <v>227</v>
+      </c>
+      <c r="I108">
         <v>1</v>
       </c>
-      <c r="G108">
-        <v>2.267783548438423</v>
-      </c>
-      <c r="H108" t="s">
-        <v>23</v>
-      </c>
-      <c r="I108">
+    </row>
+    <row r="109" spans="1:9" ht="100" customHeight="1">
+      <c r="A109">
+        <v>127</v>
+      </c>
+      <c r="B109" t="s">
+        <v>240</v>
+      </c>
+      <c r="D109" t="s">
+        <v>241</v>
+      </c>
+      <c r="E109">
+        <v>293</v>
+      </c>
+      <c r="F109">
+        <v>5</v>
+      </c>
+      <c r="G109">
+        <v>1.716814035582576</v>
+      </c>
+      <c r="H109" t="s">
+        <v>227</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="100" customHeight="1">
+      <c r="A110">
+        <v>128</v>
+      </c>
+      <c r="B110" t="s">
+        <v>242</v>
+      </c>
+      <c r="D110" t="s">
+        <v>243</v>
+      </c>
+      <c r="E110">
+        <v>248</v>
+      </c>
+      <c r="F110">
+        <v>19.5</v>
+      </c>
+      <c r="G110">
+        <v>0.6997337386092292</v>
+      </c>
+      <c r="H110" t="s">
+        <v>227</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="100" customHeight="1">
+      <c r="A111">
+        <v>129</v>
+      </c>
+      <c r="B111" t="s">
+        <v>244</v>
+      </c>
+      <c r="D111" t="s">
+        <v>245</v>
+      </c>
+      <c r="E111">
+        <v>248</v>
+      </c>
+      <c r="F111">
+        <v>52.5</v>
+      </c>
+      <c r="G111">
+        <v>-0.04939318846704208</v>
+      </c>
+      <c r="H111" t="s">
+        <v>227</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="100" customHeight="1">
+      <c r="A112">
+        <v>130</v>
+      </c>
+      <c r="B112" t="s">
+        <v>246</v>
+      </c>
+      <c r="D112" t="s">
+        <v>247</v>
+      </c>
+      <c r="E112">
+        <v>293</v>
+      </c>
+      <c r="F112">
+        <v>2</v>
+      </c>
+      <c r="G112">
+        <v>2.269203661219363</v>
+      </c>
+      <c r="H112" t="s">
+        <v>227</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="100" customHeight="1">
+      <c r="A113">
+        <v>131</v>
+      </c>
+      <c r="B113" t="s">
+        <v>248</v>
+      </c>
+      <c r="D113" t="s">
+        <v>249</v>
+      </c>
+      <c r="E113">
+        <v>238</v>
+      </c>
+      <c r="F113">
+        <v>2</v>
+      </c>
+      <c r="G113">
+        <v>1.843243929591155</v>
+      </c>
+      <c r="H113" t="s">
+        <v>250</v>
+      </c>
+      <c r="I113">
         <v>1</v>
       </c>
     </row>
